--- a/events/Prague_2015_WC/Prague_2015_WC_start.xlsx
+++ b/events/Prague_2015_WC/Prague_2015_WC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W719"/>
+  <dimension ref="A1:AC719"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1620,7 @@
           <t>LUKASS Andars</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>44865</t>
         </is>
@@ -1648,7 +1678,7 @@
           <t>PUTNINS Emils</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>63159</t>
         </is>
@@ -1706,7 +1736,7 @@
           <t>YILMAZ Emre</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>60067</t>
         </is>
@@ -1764,7 +1794,7 @@
           <t>WANG Sheng</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
@@ -1822,7 +1852,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="X26" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -1880,7 +1910,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="X27" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -1938,7 +1968,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -1996,7 +2026,7 @@
           <t>OVCHINNIKOV Aleksandr</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>39134</t>
         </is>
@@ -2054,7 +2084,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -2112,7 +2142,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -2170,7 +2200,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -2228,7 +2258,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -2286,7 +2316,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -2344,7 +2374,7 @@
           <t>CID Jesus</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>51852</t>
         </is>
@@ -2402,7 +2432,7 @@
           <t>TIMAKOV Dmitriy</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
@@ -2460,7 +2490,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -2518,7 +2548,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -2576,7 +2606,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -2634,7 +2664,7 @@
           <t>SMIRNOV Pavel</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
@@ -2745,7 +2775,7 @@
           <t>PARES Lluis</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>44008</t>
         </is>
@@ -2803,7 +2833,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -2861,7 +2891,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -2919,7 +2949,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -3030,7 +3060,7 @@
           <t>HETSMAN Anton</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>41691</t>
         </is>
@@ -3088,7 +3118,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -3146,7 +3176,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -3257,7 +3287,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -3315,7 +3345,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -3373,7 +3403,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -3431,7 +3461,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -3489,7 +3519,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -3547,7 +3577,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -3605,7 +3635,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -3663,7 +3693,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -3721,7 +3751,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -3779,7 +3809,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -3837,7 +3867,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -3895,7 +3925,7 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -3953,7 +3983,7 @@
           <t>TSAKMAKIS Christos</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>35433</t>
         </is>
@@ -4011,7 +4041,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -4069,7 +4099,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -4180,7 +4210,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -4238,7 +4268,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -4296,7 +4326,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -4354,7 +4384,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -4412,7 +4442,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -4470,7 +4500,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -4528,7 +4558,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -4586,7 +4616,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -4644,7 +4674,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -4702,7 +4732,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -4760,7 +4790,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -4818,7 +4848,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -4876,7 +4906,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -4934,7 +4964,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -4992,7 +5022,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -5050,7 +5080,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -5108,7 +5138,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -5166,7 +5196,7 @@
           <t>KRAUJA Santa</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>42927</t>
         </is>
@@ -5224,7 +5254,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -5282,7 +5312,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -5340,7 +5370,7 @@
           <t>JUETTNER Rebecca</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -5451,7 +5481,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -5509,7 +5539,7 @@
           <t>NAVEAU Laurine</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>53246</t>
         </is>
@@ -5620,7 +5650,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -5678,7 +5708,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -5736,7 +5766,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -5794,7 +5824,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -5852,7 +5882,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -5910,7 +5940,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -5968,7 +5998,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -6026,7 +6056,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -6084,7 +6114,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -6142,7 +6172,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -6200,7 +6230,7 @@
           <t>WAGNER Karolin</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>35176</t>
         </is>
@@ -6364,7 +6394,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -6422,7 +6452,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -6480,7 +6510,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -6538,7 +6568,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -6649,7 +6679,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -6760,7 +6790,7 @@
           <t>SCCHENA DIAS RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -6818,7 +6848,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -6876,7 +6906,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -6934,7 +6964,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -6992,7 +7022,7 @@
           <t>PAKERS Kaspars</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>42940</t>
         </is>
@@ -7050,7 +7080,7 @@
           <t>JANCEK Lubomir</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>35362</t>
         </is>
@@ -7108,7 +7138,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -7166,7 +7196,7 @@
           <t>CADENA Jordi</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>41644</t>
         </is>
@@ -7224,7 +7254,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -7282,7 +7312,7 @@
           <t>STRANDBERG Johan</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>35107</t>
         </is>
@@ -7340,7 +7370,7 @@
           <t>AKINYEMI Johnathan</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>36822</t>
         </is>
@@ -7398,7 +7428,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -7456,7 +7486,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -7514,7 +7544,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -7572,7 +7602,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -7630,7 +7660,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -7688,7 +7718,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -7746,7 +7776,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -7804,7 +7834,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -7862,7 +7892,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -7920,7 +7950,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -7978,7 +8008,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -8036,7 +8066,7 @@
           <t>URANO Shuhei</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>44317</t>
         </is>
@@ -8094,7 +8124,7 @@
           <t>PROZHERIN Artem</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>35775</t>
         </is>
@@ -8152,7 +8182,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -8210,7 +8240,7 @@
           <t>DAMIENS Bastien</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
@@ -8268,7 +8298,7 @@
           <t>OLAZABAL Telmo</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>38782</t>
         </is>
@@ -8326,7 +8356,7 @@
           <t>GUILLAUME Benoit</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>35418</t>
         </is>
@@ -8384,7 +8414,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -8442,7 +8472,7 @@
           <t>COLOBER Vivien</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>35233</t>
         </is>
@@ -8500,7 +8530,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -8558,7 +8588,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -8616,7 +8646,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -8674,7 +8704,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -8732,7 +8762,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -8790,7 +8820,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -8848,7 +8878,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -8906,7 +8936,7 @@
           <t>MARTIN Gerome</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>36720</t>
         </is>
@@ -8964,7 +8994,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -9022,7 +9052,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -9080,7 +9110,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -9138,7 +9168,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -9196,7 +9226,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -9254,7 +9284,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -9312,7 +9342,7 @@
           <t>SCHLAEFLI Jeremias</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>35430</t>
         </is>
@@ -9370,7 +9400,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -9428,7 +9458,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -9486,7 +9516,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -9544,7 +9574,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -9602,7 +9632,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -9660,7 +9690,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -9718,7 +9748,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -9776,7 +9806,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -9834,7 +9864,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -9945,7 +9975,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -10003,7 +10033,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -10167,7 +10197,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -10225,7 +10255,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -10283,7 +10313,7 @@
           <t>SAJBIDOR Jan</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>35236</t>
         </is>
@@ -10341,7 +10371,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -10399,7 +10429,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -10510,7 +10540,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -10621,7 +10651,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -10679,7 +10709,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -10737,7 +10767,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -10795,7 +10825,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -10853,7 +10883,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -10911,7 +10941,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -10969,7 +10999,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -11027,7 +11057,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -11085,7 +11115,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -11143,7 +11173,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -11201,7 +11231,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -11259,7 +11289,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -11317,7 +11347,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -11375,7 +11405,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -11433,7 +11463,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -11491,7 +11521,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -11549,7 +11579,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -11607,7 +11637,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -11665,7 +11695,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -11723,7 +11753,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -11781,7 +11811,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -11839,7 +11869,7 @@
           <t>LUKASS Andars</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>44865</t>
         </is>
@@ -11897,7 +11927,7 @@
           <t>PUTNINS Emils</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>63159</t>
         </is>
@@ -11955,7 +11985,7 @@
           <t>YILMAZ Emre</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>60067</t>
         </is>
@@ -12013,7 +12043,7 @@
           <t>WANG Sheng</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>60989</t>
         </is>
@@ -12071,7 +12101,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -12129,7 +12159,7 @@
           <t>CHAIDET Yutthakan</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>51798</t>
         </is>
@@ -12187,7 +12217,7 @@
           <t>LIU Chin-Han</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>51894</t>
         </is>
@@ -12245,7 +12275,7 @@
           <t>OVCHINNIKOV Aleksandr</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>39134</t>
         </is>
@@ -12303,7 +12333,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -12361,7 +12391,7 @@
           <t>DEMIRCI Ismail</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>39914</t>
         </is>
@@ -12419,7 +12449,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -12477,7 +12507,7 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -12535,7 +12565,7 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -12593,7 +12623,7 @@
           <t>CID Jesus</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>51852</t>
         </is>
@@ -12651,7 +12681,7 @@
           <t>TIMAKOV Dmitriy</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
@@ -12709,7 +12739,7 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -12767,7 +12797,7 @@
           <t>HODSON Ethan</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
@@ -12825,7 +12855,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -12883,7 +12913,7 @@
           <t>SMIRNOV Pavel</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
@@ -12994,7 +13024,7 @@
           <t>PARES Lluis</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>44008</t>
         </is>
@@ -13052,7 +13082,7 @@
           <t>WASHER Patrick</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
@@ -13110,7 +13140,7 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -13221,7 +13251,7 @@
           <t>HETSMAN Anton</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>41691</t>
         </is>
@@ -13279,7 +13309,7 @@
           <t>GIBB Benjamin</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
@@ -13337,7 +13367,7 @@
           <t>CURCEL Leonardo</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
@@ -13448,7 +13478,7 @@
           <t>IVALDI Raffaello</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>35227</t>
         </is>
@@ -13506,7 +13536,7 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -13564,7 +13594,7 @@
           <t>TRATSIAK Viktar</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35270</t>
         </is>
@@ -13622,7 +13652,7 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -13680,7 +13710,7 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -13738,7 +13768,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -13796,7 +13826,7 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -13854,7 +13884,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -13965,7 +13995,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -14023,7 +14053,7 @@
           <t>MARINIC Matija</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>35595</t>
         </is>
@@ -14081,7 +14111,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -14139,7 +14169,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -14197,7 +14227,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -14255,7 +14285,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -14313,7 +14343,7 @@
           <t>KRAUJA Santa</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>42927</t>
         </is>
@@ -14371,7 +14401,7 @@
           <t>MURZINA Juta</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>39930</t>
         </is>
@@ -14429,7 +14459,7 @@
           <t>DUANGLAHWA Atcharaporn</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>61799</t>
         </is>
@@ -14487,7 +14517,7 @@
           <t>JUETTNER Rebecca</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -14545,7 +14575,7 @@
           <t>NAVEAU Laurine</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>53246</t>
         </is>
@@ -14656,7 +14686,7 @@
           <t>JANCZY Justyna</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>43975</t>
         </is>
@@ -14714,7 +14744,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -14772,7 +14802,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -14830,7 +14860,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -14888,7 +14918,7 @@
           <t>DANIELS Haley</t>
         </is>
       </c>
-      <c r="U253" t="inlineStr">
+      <c r="X253" t="inlineStr">
         <is>
           <t>36260</t>
         </is>
@@ -14946,7 +14976,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U254" t="inlineStr">
+      <c r="X254" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -15004,7 +15034,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U255" t="inlineStr">
+      <c r="X255" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -15062,7 +15092,7 @@
           <t>SCCHENA DIAS RODRIGUES Fabio</t>
         </is>
       </c>
-      <c r="U256" t="inlineStr">
+      <c r="X256" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
@@ -15120,7 +15150,7 @@
           <t>TARKKA Teijo</t>
         </is>
       </c>
-      <c r="U257" t="inlineStr">
+      <c r="X257" t="inlineStr">
         <is>
           <t>35804</t>
         </is>
@@ -15178,7 +15208,7 @@
           <t>QUAN Xin</t>
         </is>
       </c>
-      <c r="U258" t="inlineStr">
+      <c r="X258" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
@@ -15236,7 +15266,7 @@
           <t>RASIMAVICIUS Vilius</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="X259" t="inlineStr">
         <is>
           <t>36965</t>
         </is>
@@ -15294,7 +15324,7 @@
           <t>PAKERS Kaspars</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
+      <c r="X260" t="inlineStr">
         <is>
           <t>42940</t>
         </is>
@@ -15352,7 +15382,7 @@
           <t>JANCEK Lubomir</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
+      <c r="X261" t="inlineStr">
         <is>
           <t>35362</t>
         </is>
@@ -15410,7 +15440,7 @@
           <t>ACAR Anil</t>
         </is>
       </c>
-      <c r="U262" t="inlineStr">
+      <c r="X262" t="inlineStr">
         <is>
           <t>39900</t>
         </is>
@@ -15468,7 +15498,7 @@
           <t>CADENA Jordi</t>
         </is>
       </c>
-      <c r="U263" t="inlineStr">
+      <c r="X263" t="inlineStr">
         <is>
           <t>41644</t>
         </is>
@@ -15526,7 +15556,7 @@
           <t>HELLARD Luc Suworna</t>
         </is>
       </c>
-      <c r="U264" t="inlineStr">
+      <c r="X264" t="inlineStr">
         <is>
           <t>43088</t>
         </is>
@@ -15584,7 +15614,7 @@
           <t>STRANDBERG Johan</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
+      <c r="X265" t="inlineStr">
         <is>
           <t>35107</t>
         </is>
@@ -15642,7 +15672,7 @@
           <t>AKINYEMI Johnathan</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
+      <c r="X266" t="inlineStr">
         <is>
           <t>36822</t>
         </is>
@@ -15700,7 +15730,7 @@
           <t>SHABANOV Maxim</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
+      <c r="X267" t="inlineStr">
         <is>
           <t>40575</t>
         </is>
@@ -15758,7 +15788,7 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
+      <c r="X268" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -15816,7 +15846,7 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
+      <c r="X269" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -15874,7 +15904,7 @@
           <t>ATMANAVICIUS Mantas</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
+      <c r="X270" t="inlineStr">
         <is>
           <t>35619</t>
         </is>
@@ -15932,7 +15962,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -15990,7 +16020,7 @@
           <t>TAN Ya</t>
         </is>
       </c>
-      <c r="U272" t="inlineStr">
+      <c r="X272" t="inlineStr">
         <is>
           <t>52024</t>
         </is>
@@ -16048,7 +16078,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
+      <c r="X273" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -16106,7 +16136,7 @@
           <t>SOSA Angelo</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
+      <c r="X274" t="inlineStr">
         <is>
           <t>51793</t>
         </is>
@@ -16164,7 +16194,7 @@
           <t>URANO Shuhei</t>
         </is>
       </c>
-      <c r="U275" t="inlineStr">
+      <c r="X275" t="inlineStr">
         <is>
           <t>44317</t>
         </is>
@@ -16222,7 +16252,7 @@
           <t>PROZHERIN Artem</t>
         </is>
       </c>
-      <c r="U276" t="inlineStr">
+      <c r="X276" t="inlineStr">
         <is>
           <t>35775</t>
         </is>
@@ -16280,7 +16310,7 @@
           <t>MANN Aaron</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
+      <c r="X277" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
@@ -16338,7 +16368,7 @@
           <t>OLAZABAL Telmo</t>
         </is>
       </c>
-      <c r="U278" t="inlineStr">
+      <c r="X278" t="inlineStr">
         <is>
           <t>38782</t>
         </is>
@@ -16396,7 +16426,7 @@
           <t>GUILLAUME Benoit</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
+      <c r="X279" t="inlineStr">
         <is>
           <t>35418</t>
         </is>
@@ -16454,7 +16484,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -16512,7 +16542,7 @@
           <t>COLOBER Vivien</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
+      <c r="X281" t="inlineStr">
         <is>
           <t>35233</t>
         </is>
@@ -16570,7 +16600,7 @@
           <t>ECHEVERRIA OLGUIN Andraz</t>
         </is>
       </c>
-      <c r="U282" t="inlineStr">
+      <c r="X282" t="inlineStr">
         <is>
           <t>41646</t>
         </is>
@@ -16628,7 +16658,7 @@
           <t>GASSOU Mel</t>
         </is>
       </c>
-      <c r="U283" t="inlineStr">
+      <c r="X283" t="inlineStr">
         <is>
           <t>35598</t>
         </is>
@@ -16686,7 +16716,7 @@
           <t>DAVIDSON Elliott</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
@@ -16744,7 +16774,7 @@
           <t>PEREZ Alexis</t>
         </is>
       </c>
-      <c r="U285" t="inlineStr">
+      <c r="X285" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
@@ -16802,7 +16832,7 @@
           <t>PAN Hung-Ming</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
+      <c r="X286" t="inlineStr">
         <is>
           <t>37001</t>
         </is>
@@ -16860,7 +16890,7 @@
           <t>CURTIS Samuel</t>
         </is>
       </c>
-      <c r="U287" t="inlineStr">
+      <c r="X287" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
@@ -16918,7 +16948,7 @@
           <t>ROSSI Lucas</t>
         </is>
       </c>
-      <c r="U288" t="inlineStr">
+      <c r="X288" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
@@ -16976,7 +17006,7 @@
           <t>MARTIN Gerome</t>
         </is>
       </c>
-      <c r="U289" t="inlineStr">
+      <c r="X289" t="inlineStr">
         <is>
           <t>36720</t>
         </is>
@@ -17034,7 +17064,7 @@
           <t>ROUICH Mehdi</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
+      <c r="X290" t="inlineStr">
         <is>
           <t>36944</t>
         </is>
@@ -17092,7 +17122,7 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="U291" t="inlineStr">
+      <c r="X291" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -17150,7 +17180,7 @@
           <t>MUNSCH Manuel</t>
         </is>
       </c>
-      <c r="U292" t="inlineStr">
+      <c r="X292" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
@@ -17208,7 +17238,7 @@
           <t>SEKER Enzo</t>
         </is>
       </c>
-      <c r="U293" t="inlineStr">
+      <c r="X293" t="inlineStr">
         <is>
           <t>39917</t>
         </is>
@@ -17266,7 +17296,7 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
+      <c r="X294" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -17324,7 +17354,7 @@
           <t>KANAYA Tohru</t>
         </is>
       </c>
-      <c r="U295" t="inlineStr">
+      <c r="X295" t="inlineStr">
         <is>
           <t>36484</t>
         </is>
@@ -17382,7 +17412,7 @@
           <t>SCHLAEFLI Jeremias</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
+      <c r="X296" t="inlineStr">
         <is>
           <t>35430</t>
         </is>
@@ -17440,7 +17470,7 @@
           <t>WATKINS Daniel</t>
         </is>
       </c>
-      <c r="U297" t="inlineStr">
+      <c r="X297" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -17498,7 +17528,7 @@
           <t>KARAMARKO Filip</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
+      <c r="X298" t="inlineStr">
         <is>
           <t>35596</t>
         </is>
@@ -17556,7 +17586,7 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U299" t="inlineStr">
+      <c r="X299" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -17614,7 +17644,7 @@
           <t>MRKOCI Marko</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
+      <c r="X300" t="inlineStr">
         <is>
           <t>35592</t>
         </is>
@@ -17672,7 +17702,7 @@
           <t>GILBERT Callum</t>
         </is>
       </c>
-      <c r="U301" t="inlineStr">
+      <c r="X301" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
@@ -17730,7 +17760,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
+      <c r="X302" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -17788,7 +17818,7 @@
           <t>KUDER MARUSIC Vid</t>
         </is>
       </c>
-      <c r="U303" t="inlineStr">
+      <c r="X303" t="inlineStr">
         <is>
           <t>44342</t>
         </is>
@@ -17846,7 +17876,7 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
+      <c r="X304" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -17957,7 +17987,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U306" t="inlineStr">
+      <c r="X306" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -18015,7 +18045,7 @@
           <t>SAJBIDOR Jan</t>
         </is>
       </c>
-      <c r="U307" t="inlineStr">
+      <c r="X307" t="inlineStr">
         <is>
           <t>35236</t>
         </is>
@@ -18126,7 +18156,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U309" t="inlineStr">
+      <c r="X309" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -18184,7 +18214,7 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U310" t="inlineStr">
+      <c r="X310" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -18242,7 +18272,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U311" t="inlineStr">
+      <c r="X311" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -18300,7 +18330,7 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U312" t="inlineStr">
+      <c r="X312" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -18358,7 +18388,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U313" t="inlineStr">
+      <c r="X313" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -18416,7 +18446,7 @@
           <t>GAJARDO Maritza Paz</t>
         </is>
       </c>
-      <c r="U314" t="inlineStr">
+      <c r="X314" t="inlineStr">
         <is>
           <t>60511</t>
         </is>
@@ -18474,7 +18504,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U315" t="inlineStr">
+      <c r="X315" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -18532,7 +18562,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U316" t="inlineStr">
+      <c r="X316" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -18590,7 +18620,7 @@
           <t>SMIRNOVA Polina</t>
         </is>
       </c>
-      <c r="U317" t="inlineStr">
+      <c r="X317" t="inlineStr">
         <is>
           <t>39136</t>
         </is>
@@ -18648,7 +18678,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
+      <c r="X318" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -18706,7 +18736,7 @@
           <t>EGUES Irene</t>
         </is>
       </c>
-      <c r="U319" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>51854</t>
         </is>
@@ -18764,7 +18794,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U320" t="inlineStr">
+      <c r="X320" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -18822,7 +18852,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U321" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -18880,7 +18910,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U322" t="inlineStr">
+      <c r="X322" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -18938,7 +18968,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U323" t="inlineStr">
+      <c r="X323" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -18996,7 +19026,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X324" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -19054,7 +19084,7 @@
           <t>SOLODOVNIKOVA Elena</t>
         </is>
       </c>
-      <c r="U325" t="inlineStr">
+      <c r="X325" t="inlineStr">
         <is>
           <t>35772</t>
         </is>
@@ -19112,7 +19142,7 @@
           <t>CUCHI Julia</t>
         </is>
       </c>
-      <c r="U326" t="inlineStr">
+      <c r="X326" t="inlineStr">
         <is>
           <t>35764</t>
         </is>
@@ -19170,7 +19200,7 @@
           <t>NEIME Julie</t>
         </is>
       </c>
-      <c r="U327" t="inlineStr">
+      <c r="X327" t="inlineStr">
         <is>
           <t>35679</t>
         </is>
@@ -19228,7 +19258,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U328" t="inlineStr">
+      <c r="X328" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -19286,7 +19316,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="X329" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -19397,7 +19427,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U331" t="inlineStr">
+      <c r="X331" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -19455,7 +19485,7 @@
           <t>DANGEN Haylee</t>
         </is>
       </c>
-      <c r="U332" t="inlineStr">
+      <c r="X332" t="inlineStr">
         <is>
           <t>42108</t>
         </is>
@@ -19566,7 +19596,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U334" t="inlineStr">
+      <c r="X334" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -19624,7 +19654,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U335" t="inlineStr">
+      <c r="X335" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -19682,7 +19712,7 @@
           <t>FEREKIDOU Maria</t>
         </is>
       </c>
-      <c r="U336" t="inlineStr">
+      <c r="X336" t="inlineStr">
         <is>
           <t>35434</t>
         </is>
@@ -19740,7 +19770,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U337" t="inlineStr">
+      <c r="X337" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -19798,7 +19828,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U338" t="inlineStr">
+      <c r="X338" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -19856,7 +19886,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U339" t="inlineStr">
+      <c r="X339" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -19914,7 +19944,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U340" t="inlineStr">
+      <c r="X340" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -19972,7 +20002,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U341" t="inlineStr">
+      <c r="X341" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -20030,7 +20060,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U342" t="inlineStr">
+      <c r="X342" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -20088,7 +20118,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U343" t="inlineStr">
+      <c r="X343" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -20146,7 +20176,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U344" t="inlineStr">
+      <c r="X344" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -20204,7 +20234,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U345" t="inlineStr">
+      <c r="X345" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -20262,7 +20292,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U346" t="inlineStr">
+      <c r="X346" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -20320,7 +20350,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U347" t="inlineStr">
+      <c r="X347" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -20378,7 +20408,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U348" t="inlineStr">
+      <c r="X348" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -20436,7 +20466,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U349" t="inlineStr">
+      <c r="X349" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -20494,7 +20524,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U350" t="inlineStr">
+      <c r="X350" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -20552,7 +20582,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U351" t="inlineStr">
+      <c r="X351" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -20610,7 +20640,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U352" t="inlineStr">
+      <c r="X352" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -20668,7 +20698,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U353" t="inlineStr">
+      <c r="X353" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -20779,7 +20809,7 @@
           <t>LI Lu</t>
         </is>
       </c>
-      <c r="U355" t="inlineStr">
+      <c r="X355" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
@@ -20837,7 +20867,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U356" t="inlineStr">
+      <c r="X356" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -20948,7 +20978,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U358" t="inlineStr">
+      <c r="X358" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -21006,7 +21036,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U359" t="inlineStr">
+      <c r="X359" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -21064,7 +21094,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U360" t="inlineStr">
+      <c r="X360" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -21122,7 +21152,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U361" t="inlineStr">
+      <c r="X361" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -21180,7 +21210,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U362" t="inlineStr">
+      <c r="X362" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -21238,7 +21268,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U363" t="inlineStr">
+      <c r="X363" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -21296,7 +21326,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U364" t="inlineStr">
+      <c r="X364" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -21354,7 +21384,7 @@
           <t>NEWMAN Nouria</t>
         </is>
       </c>
-      <c r="U365" t="inlineStr">
+      <c r="X365" t="inlineStr">
         <is>
           <t>35397</t>
         </is>
@@ -21465,7 +21495,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U367" t="inlineStr">
+      <c r="X367" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -21523,7 +21553,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U368" t="inlineStr">
+      <c r="X368" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -21581,7 +21611,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U369" t="inlineStr">
+      <c r="X369" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -21639,7 +21669,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U370" t="inlineStr">
+      <c r="X370" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -21697,7 +21727,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U371" t="inlineStr">
+      <c r="X371" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -21755,7 +21785,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U372" t="inlineStr">
+      <c r="X372" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -21813,7 +21843,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U373" t="inlineStr">
+      <c r="X373" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -21924,7 +21954,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U375" t="inlineStr">
+      <c r="X375" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -22045,12 +22075,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U377" t="inlineStr">
+      <c r="X377" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V377" t="inlineStr">
+      <c r="Y377" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -22113,12 +22143,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U378" t="inlineStr">
+      <c r="X378" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V378" t="inlineStr">
+      <c r="Y378" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -22181,12 +22211,12 @@
           <t>DE SOUZA Rafael</t>
         </is>
       </c>
-      <c r="U379" t="inlineStr">
+      <c r="X379" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V379" t="inlineStr">
+      <c r="Y379" t="inlineStr">
         <is>
           <t>38021</t>
         </is>
@@ -22249,12 +22279,12 @@
           <t>BOGDANOV Artem</t>
         </is>
       </c>
-      <c r="U380" t="inlineStr">
+      <c r="X380" t="inlineStr">
         <is>
           <t>39131</t>
         </is>
       </c>
-      <c r="V380" t="inlineStr">
+      <c r="Y380" t="inlineStr">
         <is>
           <t>39132</t>
         </is>
@@ -22317,12 +22347,12 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U381" t="inlineStr">
+      <c r="X381" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
       </c>
-      <c r="V381" t="inlineStr">
+      <c r="Y381" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -22385,12 +22415,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U382" t="inlineStr">
+      <c r="X382" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V382" t="inlineStr">
+      <c r="Y382" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -22453,12 +22483,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U383" t="inlineStr">
+      <c r="X383" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V383" t="inlineStr">
+      <c r="Y383" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -22521,12 +22551,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U384" t="inlineStr">
+      <c r="X384" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V384" t="inlineStr">
+      <c r="Y384" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -22589,7 +22619,7 @@
           <t>SASAKI Tsubasa</t>
         </is>
       </c>
-      <c r="U385" t="inlineStr">
+      <c r="X385" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -22652,12 +22682,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U386" t="inlineStr">
+      <c r="X386" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V386" t="inlineStr">
+      <c r="Y386" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -22720,12 +22750,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U387" t="inlineStr">
+      <c r="X387" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V387" t="inlineStr">
+      <c r="Y387" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -22788,12 +22818,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U388" t="inlineStr">
+      <c r="X388" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V388" t="inlineStr">
+      <c r="Y388" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -22856,12 +22886,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U389" t="inlineStr">
+      <c r="X389" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V389" t="inlineStr">
+      <c r="Y389" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -22924,12 +22954,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U390" t="inlineStr">
+      <c r="X390" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V390" t="inlineStr">
+      <c r="Y390" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -22992,12 +23022,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U391" t="inlineStr">
+      <c r="X391" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V391" t="inlineStr">
+      <c r="Y391" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -23060,12 +23090,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U392" t="inlineStr">
+      <c r="X392" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V392" t="inlineStr">
+      <c r="Y392" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -23128,7 +23158,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U393" t="inlineStr">
+      <c r="X393" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -23191,12 +23221,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U394" t="inlineStr">
+      <c r="X394" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V394" t="inlineStr">
+      <c r="Y394" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -23259,12 +23289,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U395" t="inlineStr">
+      <c r="X395" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V395" t="inlineStr">
+      <c r="Y395" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -23327,12 +23357,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U396" t="inlineStr">
+      <c r="X396" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V396" t="inlineStr">
+      <c r="Y396" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -23395,12 +23425,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U397" t="inlineStr">
+      <c r="X397" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V397" t="inlineStr">
+      <c r="Y397" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -23463,12 +23493,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U398" t="inlineStr">
+      <c r="X398" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V398" t="inlineStr">
+      <c r="Y398" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -23531,12 +23561,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U399" t="inlineStr">
+      <c r="X399" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V399" t="inlineStr">
+      <c r="Y399" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -23599,12 +23629,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U400" t="inlineStr">
+      <c r="X400" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V400" t="inlineStr">
+      <c r="Y400" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -23667,12 +23697,12 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U401" t="inlineStr">
+      <c r="X401" t="inlineStr">
         <is>
           <t>35351</t>
         </is>
       </c>
-      <c r="V401" t="inlineStr">
+      <c r="Y401" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -23735,12 +23765,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U402" t="inlineStr">
+      <c r="X402" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V402" t="inlineStr">
+      <c r="Y402" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -23803,12 +23833,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U403" t="inlineStr">
+      <c r="X403" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V403" t="inlineStr">
+      <c r="Y403" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -23871,12 +23901,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U404" t="inlineStr">
+      <c r="X404" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V404" t="inlineStr">
+      <c r="Y404" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -23939,12 +23969,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U405" t="inlineStr">
+      <c r="X405" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V405" t="inlineStr">
+      <c r="Y405" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -24007,7 +24037,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U406" t="inlineStr">
+      <c r="X406" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -24070,12 +24100,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U407" t="inlineStr">
+      <c r="X407" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V407" t="inlineStr">
+      <c r="Y407" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -24138,12 +24168,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U408" t="inlineStr">
+      <c r="X408" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V408" t="inlineStr">
+      <c r="Y408" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -24206,12 +24236,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U409" t="inlineStr">
+      <c r="X409" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V409" t="inlineStr">
+      <c r="Y409" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -24269,7 +24299,7 @@
           <t>GAJARDO Maritza Paz</t>
         </is>
       </c>
-      <c r="U410" t="inlineStr">
+      <c r="X410" t="inlineStr">
         <is>
           <t>60511</t>
         </is>
@@ -24327,7 +24357,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U411" t="inlineStr">
+      <c r="X411" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -24385,7 +24415,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U412" t="inlineStr">
+      <c r="X412" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -24443,7 +24473,7 @@
           <t>SMIRNOVA Polina</t>
         </is>
       </c>
-      <c r="U413" t="inlineStr">
+      <c r="X413" t="inlineStr">
         <is>
           <t>39136</t>
         </is>
@@ -24501,7 +24531,7 @@
           <t>CASSINI Maria Luz</t>
         </is>
       </c>
-      <c r="U414" t="inlineStr">
+      <c r="X414" t="inlineStr">
         <is>
           <t>41627</t>
         </is>
@@ -24559,7 +24589,7 @@
           <t>EGUES Irene</t>
         </is>
       </c>
-      <c r="U415" t="inlineStr">
+      <c r="X415" t="inlineStr">
         <is>
           <t>51854</t>
         </is>
@@ -24617,7 +24647,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U416" t="inlineStr">
+      <c r="X416" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -24675,7 +24705,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U417" t="inlineStr">
+      <c r="X417" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -24733,7 +24763,7 @@
           <t>JODAR Celia</t>
         </is>
       </c>
-      <c r="U418" t="inlineStr">
+      <c r="X418" t="inlineStr">
         <is>
           <t>36936</t>
         </is>
@@ -24791,7 +24821,7 @@
           <t>IFARRAGUERRI Anna Maria</t>
         </is>
       </c>
-      <c r="U419" t="inlineStr">
+      <c r="X419" t="inlineStr">
         <is>
           <t>39209</t>
         </is>
@@ -24849,7 +24879,7 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U420" t="inlineStr">
+      <c r="X420" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -24907,7 +24937,7 @@
           <t>SOLODOVNIKOVA Elena</t>
         </is>
       </c>
-      <c r="U421" t="inlineStr">
+      <c r="X421" t="inlineStr">
         <is>
           <t>35772</t>
         </is>
@@ -24965,7 +24995,7 @@
           <t>CUCHI Julia</t>
         </is>
       </c>
-      <c r="U422" t="inlineStr">
+      <c r="X422" t="inlineStr">
         <is>
           <t>35764</t>
         </is>
@@ -25023,7 +25053,7 @@
           <t>NEIME Julie</t>
         </is>
       </c>
-      <c r="U423" t="inlineStr">
+      <c r="X423" t="inlineStr">
         <is>
           <t>35679</t>
         </is>
@@ -25081,7 +25111,7 @@
           <t>LI Tong</t>
         </is>
       </c>
-      <c r="U424" t="inlineStr">
+      <c r="X424" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
@@ -25139,7 +25169,7 @@
           <t>REINOSO Sofia</t>
         </is>
       </c>
-      <c r="U425" t="inlineStr">
+      <c r="X425" t="inlineStr">
         <is>
           <t>45745</t>
         </is>
@@ -25250,7 +25280,7 @@
           <t>GRATWOHL Andrea</t>
         </is>
       </c>
-      <c r="U427" t="inlineStr">
+      <c r="X427" t="inlineStr">
         <is>
           <t>35429</t>
         </is>
@@ -25308,7 +25338,7 @@
           <t>DANGEN Haylee</t>
         </is>
       </c>
-      <c r="U428" t="inlineStr">
+      <c r="X428" t="inlineStr">
         <is>
           <t>42108</t>
         </is>
@@ -25419,7 +25449,7 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U430" t="inlineStr">
+      <c r="X430" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -25477,7 +25507,7 @@
           <t>FROEHLICH Thea</t>
         </is>
       </c>
-      <c r="U431" t="inlineStr">
+      <c r="X431" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
@@ -25535,7 +25565,7 @@
           <t>FEREKIDOU Maria</t>
         </is>
       </c>
-      <c r="U432" t="inlineStr">
+      <c r="X432" t="inlineStr">
         <is>
           <t>35434</t>
         </is>
@@ -25593,7 +25623,7 @@
           <t>NICHOLAS Ella</t>
         </is>
       </c>
-      <c r="U433" t="inlineStr">
+      <c r="X433" t="inlineStr">
         <is>
           <t>36591</t>
         </is>
@@ -25651,7 +25681,7 @@
           <t>CRAIG Hannah</t>
         </is>
       </c>
-      <c r="U434" t="inlineStr">
+      <c r="X434" t="inlineStr">
         <is>
           <t>35815</t>
         </is>
@@ -25709,7 +25739,7 @@
           <t>ITO Yoshika</t>
         </is>
       </c>
-      <c r="U435" t="inlineStr">
+      <c r="X435" t="inlineStr">
         <is>
           <t>36647</t>
         </is>
@@ -25767,7 +25797,7 @@
           <t>ISMAILOVA Sevinch</t>
         </is>
       </c>
-      <c r="U436" t="inlineStr">
+      <c r="X436" t="inlineStr">
         <is>
           <t>35269</t>
         </is>
@@ -25825,7 +25855,7 @@
           <t>GROENEVELD Jessica</t>
         </is>
       </c>
-      <c r="U437" t="inlineStr">
+      <c r="X437" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
@@ -25883,7 +25913,7 @@
           <t>SABATTINI Chiara</t>
         </is>
       </c>
-      <c r="U438" t="inlineStr">
+      <c r="X438" t="inlineStr">
         <is>
           <t>35219</t>
         </is>
@@ -25941,7 +25971,7 @@
           <t>NEE Ashley</t>
         </is>
       </c>
-      <c r="U439" t="inlineStr">
+      <c r="X439" t="inlineStr">
         <is>
           <t>36363</t>
         </is>
@@ -25999,7 +26029,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U440" t="inlineStr">
+      <c r="X440" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -26057,7 +26087,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U441" t="inlineStr">
+      <c r="X441" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -26115,7 +26145,7 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U442" t="inlineStr">
+      <c r="X442" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -26173,7 +26203,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U443" t="inlineStr">
+      <c r="X443" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -26231,7 +26261,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U444" t="inlineStr">
+      <c r="X444" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -26289,7 +26319,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U445" t="inlineStr">
+      <c r="X445" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -26347,7 +26377,7 @@
           <t>LI Lu</t>
         </is>
       </c>
-      <c r="U446" t="inlineStr">
+      <c r="X446" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
@@ -26405,7 +26435,7 @@
           <t>JONES Luuka</t>
         </is>
       </c>
-      <c r="U447" t="inlineStr">
+      <c r="X447" t="inlineStr">
         <is>
           <t>36657</t>
         </is>
@@ -26463,7 +26493,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U448" t="inlineStr">
+      <c r="X448" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -26521,7 +26551,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U449" t="inlineStr">
+      <c r="X449" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -26579,7 +26609,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U450" t="inlineStr">
+      <c r="X450" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -26690,7 +26720,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U452" t="inlineStr">
+      <c r="X452" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -26753,12 +26783,12 @@
           <t>DENNIS Tad</t>
         </is>
       </c>
-      <c r="U453" t="inlineStr">
+      <c r="X453" t="inlineStr">
         <is>
           <t>51904</t>
         </is>
       </c>
-      <c r="V453" t="inlineStr">
+      <c r="Y453" t="inlineStr">
         <is>
           <t>42253</t>
         </is>
@@ -26821,12 +26851,12 @@
           <t>SILVA Jose</t>
         </is>
       </c>
-      <c r="U454" t="inlineStr">
+      <c r="X454" t="inlineStr">
         <is>
           <t>41649</t>
         </is>
       </c>
-      <c r="V454" t="inlineStr">
+      <c r="Y454" t="inlineStr">
         <is>
           <t>36494</t>
         </is>
@@ -26889,12 +26919,12 @@
           <t>DE SOUZA Rafael</t>
         </is>
       </c>
-      <c r="U455" t="inlineStr">
+      <c r="X455" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V455" t="inlineStr">
+      <c r="Y455" t="inlineStr">
         <is>
           <t>38021</t>
         </is>
@@ -26957,12 +26987,12 @@
           <t>BOGDANOV Artem</t>
         </is>
       </c>
-      <c r="U456" t="inlineStr">
+      <c r="X456" t="inlineStr">
         <is>
           <t>39131</t>
         </is>
       </c>
-      <c r="V456" t="inlineStr">
+      <c r="Y456" t="inlineStr">
         <is>
           <t>39132</t>
         </is>
@@ -27025,12 +27055,12 @@
           <t>ROSSI Sebastian</t>
         </is>
       </c>
-      <c r="U457" t="inlineStr">
+      <c r="X457" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
       </c>
-      <c r="V457" t="inlineStr">
+      <c r="Y457" t="inlineStr">
         <is>
           <t>36915</t>
         </is>
@@ -27093,12 +27123,12 @@
           <t>SMEDLEY Cameron</t>
         </is>
       </c>
-      <c r="U458" t="inlineStr">
+      <c r="X458" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V458" t="inlineStr">
+      <c r="Y458" t="inlineStr">
         <is>
           <t>35543</t>
         </is>
@@ -27161,12 +27191,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U459" t="inlineStr">
+      <c r="X459" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V459" t="inlineStr">
+      <c r="Y459" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -27229,12 +27259,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U460" t="inlineStr">
+      <c r="X460" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V460" t="inlineStr">
+      <c r="Y460" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -27297,7 +27327,7 @@
           <t>SASAKI Tsubasa</t>
         </is>
       </c>
-      <c r="U461" t="inlineStr">
+      <c r="X461" t="inlineStr">
         <is>
           <t>41610</t>
         </is>
@@ -27360,12 +27390,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U462" t="inlineStr">
+      <c r="X462" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V462" t="inlineStr">
+      <c r="Y462" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -27428,12 +27458,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U463" t="inlineStr">
+      <c r="X463" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V463" t="inlineStr">
+      <c r="Y463" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -27496,12 +27526,12 @@
           <t>KERVELLA Loic</t>
         </is>
       </c>
-      <c r="U464" t="inlineStr">
+      <c r="X464" t="inlineStr">
         <is>
           <t>35671</t>
         </is>
       </c>
-      <c r="V464" t="inlineStr">
+      <c r="Y464" t="inlineStr">
         <is>
           <t>35672</t>
         </is>
@@ -27564,12 +27594,12 @@
           <t>OLIVEIRA Anderson</t>
         </is>
       </c>
-      <c r="U465" t="inlineStr">
+      <c r="X465" t="inlineStr">
         <is>
           <t>38018</t>
         </is>
       </c>
-      <c r="V465" t="inlineStr">
+      <c r="Y465" t="inlineStr">
         <is>
           <t>38020</t>
         </is>
@@ -27632,12 +27662,12 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U466" t="inlineStr">
+      <c r="X466" t="inlineStr">
         <is>
           <t>35068</t>
         </is>
       </c>
-      <c r="V466" t="inlineStr">
+      <c r="Y466" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -27700,7 +27730,7 @@
           <t>PITT Greg</t>
         </is>
       </c>
-      <c r="U467" t="inlineStr">
+      <c r="X467" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -27763,12 +27793,12 @@
           <t>FERRARI Niccolo</t>
         </is>
       </c>
-      <c r="U468" t="inlineStr">
+      <c r="X468" t="inlineStr">
         <is>
           <t>35497</t>
         </is>
       </c>
-      <c r="V468" t="inlineStr">
+      <c r="Y468" t="inlineStr">
         <is>
           <t>35498</t>
         </is>
@@ -27831,12 +27861,12 @@
           <t>MUELLER Kevin</t>
         </is>
       </c>
-      <c r="U469" t="inlineStr">
+      <c r="X469" t="inlineStr">
         <is>
           <t>35148</t>
         </is>
       </c>
-      <c r="V469" t="inlineStr">
+      <c r="Y469" t="inlineStr">
         <is>
           <t>35149</t>
         </is>
@@ -27899,12 +27929,12 @@
           <t>BRZEZINSKI Andrzej</t>
         </is>
       </c>
-      <c r="U470" t="inlineStr">
+      <c r="X470" t="inlineStr">
         <is>
           <t>35082</t>
         </is>
       </c>
-      <c r="V470" t="inlineStr">
+      <c r="Y470" t="inlineStr">
         <is>
           <t>35081</t>
         </is>
@@ -27967,12 +27997,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U471" t="inlineStr">
+      <c r="X471" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V471" t="inlineStr">
+      <c r="Y471" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -28348,7 +28378,7 @@
           <t>LENARCIC Jure</t>
         </is>
       </c>
-      <c r="U478" t="inlineStr">
+      <c r="X478" t="inlineStr">
         <is>
           <t>36259</t>
         </is>
@@ -28406,7 +28436,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U479" t="inlineStr">
+      <c r="X479" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -28464,7 +28494,7 @@
           <t>HEDWIG Grzegorz</t>
         </is>
       </c>
-      <c r="U480" t="inlineStr">
+      <c r="X480" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
@@ -28522,7 +28552,7 @@
           <t>OVCHINNIKOV Aleksandr</t>
         </is>
       </c>
-      <c r="U481" t="inlineStr">
+      <c r="X481" t="inlineStr">
         <is>
           <t>39134</t>
         </is>
@@ -28580,7 +28610,7 @@
           <t>EICHFELD Casey</t>
         </is>
       </c>
-      <c r="U482" t="inlineStr">
+      <c r="X482" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
@@ -28638,7 +28668,7 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U483" t="inlineStr">
+      <c r="X483" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -28696,7 +28726,7 @@
           <t>GONDEK Kacper</t>
         </is>
       </c>
-      <c r="U484" t="inlineStr">
+      <c r="X484" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
@@ -28754,7 +28784,7 @@
           <t>MASEK Jan</t>
         </is>
       </c>
-      <c r="U485" t="inlineStr">
+      <c r="X485" t="inlineStr">
         <is>
           <t>36013</t>
         </is>
@@ -28812,7 +28842,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U486" t="inlineStr">
+      <c r="X486" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -28870,7 +28900,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U487" t="inlineStr">
+      <c r="X487" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -28928,7 +28958,7 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U488" t="inlineStr">
+      <c r="X488" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -28986,7 +29016,7 @@
           <t>CECCON Paolo</t>
         </is>
       </c>
-      <c r="U489" t="inlineStr">
+      <c r="X489" t="inlineStr">
         <is>
           <t>39903</t>
         </is>
@@ -29044,7 +29074,7 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U490" t="inlineStr">
+      <c r="X490" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -29102,7 +29132,7 @@
           <t>WESTLEY Ryan</t>
         </is>
       </c>
-      <c r="U491" t="inlineStr">
+      <c r="X491" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
@@ -29160,7 +29190,7 @@
           <t>CIPRESSI Stefano</t>
         </is>
       </c>
-      <c r="U492" t="inlineStr">
+      <c r="X492" t="inlineStr">
         <is>
           <t>35495</t>
         </is>
@@ -29218,7 +29248,7 @@
           <t>TSAKMAKIS Christos</t>
         </is>
       </c>
-      <c r="U493" t="inlineStr">
+      <c r="X493" t="inlineStr">
         <is>
           <t>35433</t>
         </is>
@@ -29276,7 +29306,7 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U494" t="inlineStr">
+      <c r="X494" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -29334,7 +29364,7 @@
           <t>JEFFERY Robin</t>
         </is>
       </c>
-      <c r="U495" t="inlineStr">
+      <c r="X495" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
@@ -29392,7 +29422,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U496" t="inlineStr">
+      <c r="X496" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -29450,7 +29480,7 @@
           <t>HANEDA Takuya</t>
         </is>
       </c>
-      <c r="U497" t="inlineStr">
+      <c r="X497" t="inlineStr">
         <is>
           <t>36481</t>
         </is>
@@ -29508,7 +29538,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U498" t="inlineStr">
+      <c r="X498" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -29566,7 +29596,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U499" t="inlineStr">
+      <c r="X499" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -29624,7 +29654,7 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U500" t="inlineStr">
+      <c r="X500" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -29682,7 +29712,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U501" t="inlineStr">
+      <c r="X501" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -29740,7 +29770,7 @@
           <t>JANE Michal</t>
         </is>
       </c>
-      <c r="U502" t="inlineStr">
+      <c r="X502" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
@@ -29798,7 +29828,7 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U503" t="inlineStr">
+      <c r="X503" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -29856,7 +29886,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U504" t="inlineStr">
+      <c r="X504" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -29914,7 +29944,7 @@
           <t>TILLARD Pierre-Antoine</t>
         </is>
       </c>
-      <c r="U505" t="inlineStr">
+      <c r="X505" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
@@ -29972,7 +30002,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U506" t="inlineStr">
+      <c r="X506" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -30030,7 +30060,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U507" t="inlineStr">
+      <c r="X507" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -30088,7 +30118,7 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="U508" t="inlineStr">
+      <c r="X508" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -30146,7 +30176,7 @@
           <t>SABITOVA Zulfia</t>
         </is>
       </c>
-      <c r="U509" t="inlineStr">
+      <c r="X509" t="inlineStr">
         <is>
           <t>40572</t>
         </is>
@@ -30204,7 +30234,7 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U510" t="inlineStr">
+      <c r="X510" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -30262,7 +30292,7 @@
           <t>DOBROTVORSKA Viktoriia</t>
         </is>
       </c>
-      <c r="U511" t="inlineStr">
+      <c r="X511" t="inlineStr">
         <is>
           <t>35526</t>
         </is>
@@ -30320,7 +30350,7 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U512" t="inlineStr">
+      <c r="X512" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -30378,7 +30408,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U513" t="inlineStr">
+      <c r="X513" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -30489,7 +30519,7 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U515" t="inlineStr">
+      <c r="X515" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -30600,7 +30630,7 @@
           <t>WAGNER Karolin</t>
         </is>
       </c>
-      <c r="U517" t="inlineStr">
+      <c r="X517" t="inlineStr">
         <is>
           <t>35176</t>
         </is>
@@ -30764,7 +30794,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U520" t="inlineStr">
+      <c r="X520" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -30822,7 +30852,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U521" t="inlineStr">
+      <c r="X521" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -30880,7 +30910,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U522" t="inlineStr">
+      <c r="X522" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -30938,7 +30968,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U523" t="inlineStr">
+      <c r="X523" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -30996,7 +31026,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U524" t="inlineStr">
+      <c r="X524" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -31054,7 +31084,7 @@
           <t>US Viktoriia</t>
         </is>
       </c>
-      <c r="U525" t="inlineStr">
+      <c r="X525" t="inlineStr">
         <is>
           <t>35528</t>
         </is>
@@ -31112,7 +31142,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U526" t="inlineStr">
+      <c r="X526" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -31223,7 +31253,7 @@
           <t>LLORENTE David</t>
         </is>
       </c>
-      <c r="U528" t="inlineStr">
+      <c r="X528" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
@@ -31334,7 +31364,7 @@
           <t>POWELL Richard</t>
         </is>
       </c>
-      <c r="U530" t="inlineStr">
+      <c r="X530" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
@@ -31445,7 +31475,7 @@
           <t>KAUZER Peter</t>
         </is>
       </c>
-      <c r="U532" t="inlineStr">
+      <c r="X532" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
@@ -31503,7 +31533,7 @@
           <t>POTOCNY Marcel</t>
         </is>
       </c>
-      <c r="U533" t="inlineStr">
+      <c r="X533" t="inlineStr">
         <is>
           <t>35235</t>
         </is>
@@ -31614,7 +31644,7 @@
           <t>BERSINGER Thomas</t>
         </is>
       </c>
-      <c r="U535" t="inlineStr">
+      <c r="X535" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
@@ -31672,7 +31702,7 @@
           <t>PETERLIN Janos</t>
         </is>
       </c>
-      <c r="U536" t="inlineStr">
+      <c r="X536" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
@@ -31730,7 +31760,7 @@
           <t>OKREGLAK Maciej</t>
         </is>
       </c>
-      <c r="U537" t="inlineStr">
+      <c r="X537" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
@@ -31841,7 +31871,7 @@
           <t>MAXEINER Tim</t>
         </is>
       </c>
-      <c r="U539" t="inlineStr">
+      <c r="X539" t="inlineStr">
         <is>
           <t>35117</t>
         </is>
@@ -31899,7 +31929,7 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U540" t="inlineStr">
+      <c r="X540" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -31957,7 +31987,7 @@
           <t>TAYLER Michael</t>
         </is>
       </c>
-      <c r="U541" t="inlineStr">
+      <c r="X541" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
@@ -32015,7 +32045,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U542" t="inlineStr">
+      <c r="X542" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -32073,7 +32103,7 @@
           <t>MEGLIC Jure</t>
         </is>
       </c>
-      <c r="U543" t="inlineStr">
+      <c r="X543" t="inlineStr">
         <is>
           <t>35590</t>
         </is>
@@ -32131,7 +32161,7 @@
           <t>HAYWARD Ben</t>
         </is>
       </c>
-      <c r="U544" t="inlineStr">
+      <c r="X544" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
@@ -32189,7 +32219,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U545" t="inlineStr">
+      <c r="X545" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -32247,7 +32277,7 @@
           <t>OBLINGER Helmut</t>
         </is>
       </c>
-      <c r="U546" t="inlineStr">
+      <c r="X546" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
@@ -32305,7 +32335,7 @@
           <t>ROMEO Andrea</t>
         </is>
       </c>
-      <c r="U547" t="inlineStr">
+      <c r="X547" t="inlineStr">
         <is>
           <t>35502</t>
         </is>
@@ -32363,7 +32393,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U548" t="inlineStr">
+      <c r="X548" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -32421,7 +32451,7 @@
           <t>ADACHI Kazuya</t>
         </is>
       </c>
-      <c r="U549" t="inlineStr">
+      <c r="X549" t="inlineStr">
         <is>
           <t>36646</t>
         </is>
@@ -32479,7 +32509,7 @@
           <t>SCHUBERT Sebastian</t>
         </is>
       </c>
-      <c r="U550" t="inlineStr">
+      <c r="X550" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
@@ -32537,7 +32567,7 @@
           <t>DELFOUR Lucien</t>
         </is>
       </c>
-      <c r="U551" t="inlineStr">
+      <c r="X551" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
@@ -32595,7 +32625,7 @@
           <t>LEITNER Mario</t>
         </is>
       </c>
-      <c r="U552" t="inlineStr">
+      <c r="X552" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
@@ -32653,7 +32683,7 @@
           <t>DOBY Mathieu</t>
         </is>
       </c>
-      <c r="U553" t="inlineStr">
+      <c r="X553" t="inlineStr">
         <is>
           <t>35292</t>
         </is>
@@ -32711,7 +32741,7 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="U554" t="inlineStr">
+      <c r="X554" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -32769,7 +32799,7 @@
           <t>HILGERT Lubos</t>
         </is>
       </c>
-      <c r="U555" t="inlineStr">
+      <c r="X555" t="inlineStr">
         <is>
           <t>35032</t>
         </is>
@@ -32827,7 +32857,7 @@
           <t>AIGNER Hannes</t>
         </is>
       </c>
-      <c r="U556" t="inlineStr">
+      <c r="X556" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
@@ -32885,7 +32915,7 @@
           <t>DE GENNARO Giovanni</t>
         </is>
       </c>
-      <c r="U557" t="inlineStr">
+      <c r="X557" t="inlineStr">
         <is>
           <t>35244</t>
         </is>
@@ -32943,7 +32973,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U558" t="inlineStr">
+      <c r="X558" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -33001,7 +33031,7 @@
           <t>DAMIENS Bastien</t>
         </is>
       </c>
-      <c r="U559" t="inlineStr">
+      <c r="X559" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
@@ -33059,7 +33089,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U560" t="inlineStr">
+      <c r="X560" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -33117,7 +33147,7 @@
           <t>TSVIET Igor</t>
         </is>
       </c>
-      <c r="U561" t="inlineStr">
+      <c r="X561" t="inlineStr">
         <is>
           <t>35527</t>
         </is>
@@ -33175,7 +33205,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U562" t="inlineStr">
+      <c r="X562" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -33233,7 +33263,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U563" t="inlineStr">
+      <c r="X563" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -33291,7 +33321,7 @@
           <t>HALCIN Martin</t>
         </is>
       </c>
-      <c r="U564" t="inlineStr">
+      <c r="X564" t="inlineStr">
         <is>
           <t>35355</t>
         </is>
@@ -33349,7 +33379,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U565" t="inlineStr">
+      <c r="X565" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -33407,7 +33437,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U566" t="inlineStr">
+      <c r="X566" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -33528,7 +33558,7 @@
           <t>SLAFKOVSKY Alexander</t>
         </is>
       </c>
-      <c r="U568" t="inlineStr">
+      <c r="X568" t="inlineStr">
         <is>
           <t>35129</t>
         </is>
@@ -33596,7 +33626,7 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U569" t="inlineStr">
+      <c r="X569" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -33664,7 +33694,7 @@
           <t>SAVSEK Benjamin</t>
         </is>
       </c>
-      <c r="U570" t="inlineStr">
+      <c r="X570" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
@@ -33732,7 +33762,7 @@
           <t>GARGAUD CHANUT Denis</t>
         </is>
       </c>
-      <c r="U571" t="inlineStr">
+      <c r="X571" t="inlineStr">
         <is>
           <t>35177</t>
         </is>
@@ -33800,7 +33830,7 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U572" t="inlineStr">
+      <c r="X572" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -33868,7 +33898,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U573" t="inlineStr">
+      <c r="X573" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -33936,7 +33966,7 @@
           <t>FLORENCE David</t>
         </is>
       </c>
-      <c r="U574" t="inlineStr">
+      <c r="X574" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -34004,7 +34034,7 @@
           <t>BOZIC Luka</t>
         </is>
       </c>
-      <c r="U575" t="inlineStr">
+      <c r="X575" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
@@ -34072,7 +34102,7 @@
           <t>TASIADIS Sideris</t>
         </is>
       </c>
-      <c r="U576" t="inlineStr">
+      <c r="X576" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
@@ -34140,7 +34170,7 @@
           <t>JEZEK Stanislav</t>
         </is>
       </c>
-      <c r="U577" t="inlineStr">
+      <c r="X577" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
@@ -34208,7 +34238,7 @@
           <t>BAUDU Lucie</t>
         </is>
       </c>
-      <c r="U578" t="inlineStr">
+      <c r="X578" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
@@ -34276,7 +34306,7 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U579" t="inlineStr">
+      <c r="X579" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -34407,7 +34437,7 @@
           <t>STOECKLIN Lena</t>
         </is>
       </c>
-      <c r="U581" t="inlineStr">
+      <c r="X581" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
@@ -34601,7 +34631,7 @@
           <t>SCHMID Julia</t>
         </is>
       </c>
-      <c r="U584" t="inlineStr">
+      <c r="X584" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
@@ -34669,7 +34699,7 @@
           <t>JANCOVA Monika</t>
         </is>
       </c>
-      <c r="U585" t="inlineStr">
+      <c r="X585" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -34737,7 +34767,7 @@
           <t>WOLFFHARDT Viktoria</t>
         </is>
       </c>
-      <c r="U586" t="inlineStr">
+      <c r="X586" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
@@ -34868,7 +34898,7 @@
           <t>MOLMENTI Daniele</t>
         </is>
       </c>
-      <c r="U588" t="inlineStr">
+      <c r="X588" t="inlineStr">
         <is>
           <t>42017</t>
         </is>
@@ -34936,7 +34966,7 @@
           <t>OHRSTROM Isak</t>
         </is>
       </c>
-      <c r="U589" t="inlineStr">
+      <c r="X589" t="inlineStr">
         <is>
           <t>35101</t>
         </is>
@@ -34994,7 +35024,7 @@
           <t>CLARKE Joseph</t>
         </is>
       </c>
-      <c r="U590" t="inlineStr">
+      <c r="X590" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
@@ -35062,7 +35092,7 @@
           <t>HRADILEK Vavrinec</t>
         </is>
       </c>
-      <c r="U591" t="inlineStr">
+      <c r="X591" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
@@ -35193,7 +35223,7 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U593" t="inlineStr">
+      <c r="X593" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -35261,7 +35291,7 @@
           <t>POLACZYK Mateusz</t>
         </is>
       </c>
-      <c r="U594" t="inlineStr">
+      <c r="X594" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
@@ -35329,7 +35359,7 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U595" t="inlineStr">
+      <c r="X595" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -35397,7 +35427,7 @@
           <t>PRSKAVEC Jiri</t>
         </is>
       </c>
-      <c r="U596" t="inlineStr">
+      <c r="X596" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
@@ -35465,7 +35495,7 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U597" t="inlineStr">
+      <c r="X597" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -35543,17 +35573,17 @@
           <t>HIGGINS Shaun</t>
         </is>
       </c>
-      <c r="U598" t="inlineStr">
+      <c r="X598" t="inlineStr">
         <is>
           <t>36711</t>
         </is>
       </c>
-      <c r="V598" t="inlineStr">
+      <c r="Y598" t="inlineStr">
         <is>
           <t>42081</t>
         </is>
       </c>
-      <c r="W598" t="inlineStr">
+      <c r="Z598" t="inlineStr">
         <is>
           <t>36655</t>
         </is>
@@ -35631,12 +35661,12 @@
           <t>SERRA Thiago</t>
         </is>
       </c>
-      <c r="U599" t="inlineStr">
+      <c r="X599" t="inlineStr">
         <is>
           <t>38014</t>
         </is>
       </c>
-      <c r="W599" t="inlineStr">
+      <c r="Z599" t="inlineStr">
         <is>
           <t>41647</t>
         </is>
@@ -35714,17 +35744,17 @@
           <t>SZTUBA Igor</t>
         </is>
       </c>
-      <c r="U600" t="inlineStr">
+      <c r="X600" t="inlineStr">
         <is>
           <t>35465</t>
         </is>
       </c>
-      <c r="V600" t="inlineStr">
+      <c r="Y600" t="inlineStr">
         <is>
           <t>35472</t>
         </is>
       </c>
-      <c r="W600" t="inlineStr">
+      <c r="Z600" t="inlineStr">
         <is>
           <t>35087</t>
         </is>
@@ -35802,17 +35832,17 @@
           <t>BORROWS Ian</t>
         </is>
       </c>
-      <c r="U601" t="inlineStr">
+      <c r="X601" t="inlineStr">
         <is>
           <t>36525</t>
         </is>
       </c>
-      <c r="V601" t="inlineStr">
+      <c r="Y601" t="inlineStr">
         <is>
           <t>38437</t>
         </is>
       </c>
-      <c r="W601" t="inlineStr">
+      <c r="Z601" t="inlineStr">
         <is>
           <t>36534</t>
         </is>
@@ -35890,17 +35920,17 @@
           <t>TIMAKOV Dmitriy</t>
         </is>
       </c>
-      <c r="U602" t="inlineStr">
+      <c r="X602" t="inlineStr">
         <is>
           <t>39134</t>
         </is>
       </c>
-      <c r="V602" t="inlineStr">
+      <c r="Y602" t="inlineStr">
         <is>
           <t>39135</t>
         </is>
       </c>
-      <c r="W602" t="inlineStr">
+      <c r="Z602" t="inlineStr">
         <is>
           <t>53527</t>
         </is>
@@ -35978,12 +36008,12 @@
           <t>LOKKEN Zachary</t>
         </is>
       </c>
-      <c r="U603" t="inlineStr">
+      <c r="X603" t="inlineStr">
         <is>
           <t>35067</t>
         </is>
       </c>
-      <c r="W603" t="inlineStr">
+      <c r="Z603" t="inlineStr">
         <is>
           <t>35069</t>
         </is>
@@ -36061,17 +36091,17 @@
           <t>BURGESS Adam</t>
         </is>
       </c>
-      <c r="U604" t="inlineStr">
+      <c r="X604" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
       </c>
-      <c r="V604" t="inlineStr">
+      <c r="Y604" t="inlineStr">
         <is>
           <t>35651</t>
         </is>
       </c>
-      <c r="W604" t="inlineStr">
+      <c r="Z604" t="inlineStr">
         <is>
           <t>35647</t>
         </is>
@@ -36149,17 +36179,17 @@
           <t>ANTON Franz</t>
         </is>
       </c>
-      <c r="U605" t="inlineStr">
+      <c r="X605" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
       </c>
-      <c r="V605" t="inlineStr">
+      <c r="Y605" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
       </c>
-      <c r="W605" t="inlineStr">
+      <c r="Z605" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
@@ -36237,17 +36267,17 @@
           <t>RAK Tomas</t>
         </is>
       </c>
-      <c r="U606" t="inlineStr">
+      <c r="X606" t="inlineStr">
         <is>
           <t>35059</t>
         </is>
       </c>
-      <c r="V606" t="inlineStr">
+      <c r="Y606" t="inlineStr">
         <is>
           <t>35037</t>
         </is>
       </c>
-      <c r="W606" t="inlineStr">
+      <c r="Z606" t="inlineStr">
         <is>
           <t>35056</t>
         </is>
@@ -36325,17 +36355,17 @@
           <t>THOMAS Martin</t>
         </is>
       </c>
-      <c r="U607" t="inlineStr">
+      <c r="X607" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
       </c>
-      <c r="V607" t="inlineStr">
+      <c r="Y607" t="inlineStr">
         <is>
           <t>35413</t>
         </is>
       </c>
-      <c r="W607" t="inlineStr">
+      <c r="Z607" t="inlineStr">
         <is>
           <t>35412</t>
         </is>
@@ -36413,17 +36443,17 @@
           <t>BERCIC Anze</t>
         </is>
       </c>
-      <c r="U608" t="inlineStr">
+      <c r="X608" t="inlineStr">
         <is>
           <t>36218</t>
         </is>
       </c>
-      <c r="V608" t="inlineStr">
+      <c r="Y608" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="W608" t="inlineStr">
+      <c r="Z608" t="inlineStr">
         <is>
           <t>36253</t>
         </is>
@@ -36501,17 +36531,17 @@
           <t>WERATSCHNIG Nadine</t>
         </is>
       </c>
-      <c r="U609" t="inlineStr">
+      <c r="X609" t="inlineStr">
         <is>
           <t>35309</t>
         </is>
       </c>
-      <c r="V609" t="inlineStr">
+      <c r="Y609" t="inlineStr">
         <is>
           <t>35303</t>
         </is>
       </c>
-      <c r="W609" t="inlineStr">
+      <c r="Z609" t="inlineStr">
         <is>
           <t>41613</t>
         </is>
@@ -36589,7 +36619,7 @@
           <t>FISEROVA Tereza</t>
         </is>
       </c>
-      <c r="V610" t="inlineStr">
+      <c r="Y610" t="inlineStr">
         <is>
           <t>36015</t>
         </is>
@@ -36657,12 +36687,12 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="V611" t="inlineStr">
+      <c r="Y611" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
       </c>
-      <c r="W611" t="inlineStr">
+      <c r="Z611" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -36740,17 +36770,17 @@
           <t>JUETTNER Rebecca</t>
         </is>
       </c>
-      <c r="U612" t="inlineStr">
+      <c r="X612" t="inlineStr">
         <is>
           <t>35176</t>
         </is>
       </c>
-      <c r="V612" t="inlineStr">
+      <c r="Y612" t="inlineStr">
         <is>
           <t>35822</t>
         </is>
       </c>
-      <c r="W612" t="inlineStr">
+      <c r="Z612" t="inlineStr">
         <is>
           <t>51836</t>
         </is>
@@ -36828,17 +36858,17 @@
           <t>TIXIER Cecile</t>
         </is>
       </c>
-      <c r="U613" t="inlineStr">
+      <c r="X613" t="inlineStr">
         <is>
           <t>35669</t>
         </is>
       </c>
-      <c r="V613" t="inlineStr">
+      <c r="Y613" t="inlineStr">
         <is>
           <t>53246</t>
         </is>
       </c>
-      <c r="W613" t="inlineStr">
+      <c r="Z613" t="inlineStr">
         <is>
           <t>35687</t>
         </is>
@@ -36916,17 +36946,17 @@
           <t>RYAN Cade</t>
         </is>
       </c>
-      <c r="U614" t="inlineStr">
+      <c r="X614" t="inlineStr">
         <is>
           <t>36683</t>
         </is>
       </c>
-      <c r="V614" t="inlineStr">
+      <c r="Y614" t="inlineStr">
         <is>
           <t>43077</t>
         </is>
       </c>
-      <c r="W614" t="inlineStr">
+      <c r="Z614" t="inlineStr">
         <is>
           <t>37919</t>
         </is>
@@ -37004,17 +37034,17 @@
           <t>CORTEZ Geronimo</t>
         </is>
       </c>
-      <c r="U615" t="inlineStr">
+      <c r="X615" t="inlineStr">
         <is>
           <t>35228</t>
         </is>
       </c>
-      <c r="V615" t="inlineStr">
+      <c r="Y615" t="inlineStr">
         <is>
           <t>36925</t>
         </is>
       </c>
-      <c r="W615" t="inlineStr">
+      <c r="Z615" t="inlineStr">
         <is>
           <t>51835</t>
         </is>
@@ -37092,12 +37122,12 @@
           <t>MARTINS TAQUES Ricardo</t>
         </is>
       </c>
-      <c r="V616" t="inlineStr">
+      <c r="Y616" t="inlineStr">
         <is>
           <t>38023</t>
         </is>
       </c>
-      <c r="W616" t="inlineStr">
+      <c r="Z616" t="inlineStr">
         <is>
           <t>38022</t>
         </is>
@@ -37175,12 +37205,12 @@
           <t>BUTCHER Finn</t>
         </is>
       </c>
-      <c r="V617" t="inlineStr">
+      <c r="Y617" t="inlineStr">
         <is>
           <t>42090</t>
         </is>
       </c>
-      <c r="W617" t="inlineStr">
+      <c r="Z617" t="inlineStr">
         <is>
           <t>36663</t>
         </is>
@@ -37258,17 +37288,17 @@
           <t>FORD David</t>
         </is>
       </c>
-      <c r="U618" t="inlineStr">
+      <c r="X618" t="inlineStr">
         <is>
           <t>35539</t>
         </is>
       </c>
-      <c r="V618" t="inlineStr">
+      <c r="Y618" t="inlineStr">
         <is>
           <t>36262</t>
         </is>
       </c>
-      <c r="W618" t="inlineStr">
+      <c r="Z618" t="inlineStr">
         <is>
           <t>35532</t>
         </is>
@@ -37346,12 +37376,12 @@
           <t>FORBES-CRYANS Bradley</t>
         </is>
       </c>
-      <c r="V619" t="inlineStr">
+      <c r="Y619" t="inlineStr">
         <is>
           <t>35654</t>
         </is>
       </c>
-      <c r="W619" t="inlineStr">
+      <c r="Z619" t="inlineStr">
         <is>
           <t>36513</t>
         </is>
@@ -37429,17 +37459,17 @@
           <t>MARTIN Gerome</t>
         </is>
       </c>
-      <c r="U620" t="inlineStr">
+      <c r="X620" t="inlineStr">
         <is>
           <t>35430</t>
         </is>
       </c>
-      <c r="V620" t="inlineStr">
+      <c r="Y620" t="inlineStr">
         <is>
           <t>35631</t>
         </is>
       </c>
-      <c r="W620" t="inlineStr">
+      <c r="Z620" t="inlineStr">
         <is>
           <t>36720</t>
         </is>
@@ -37507,17 +37537,17 @@
           <t>OSCHMAUTZ Felix</t>
         </is>
       </c>
-      <c r="U621" t="inlineStr">
+      <c r="X621" t="inlineStr">
         <is>
           <t>35546</t>
         </is>
       </c>
-      <c r="V621" t="inlineStr">
+      <c r="Y621" t="inlineStr">
         <is>
           <t>35281</t>
         </is>
       </c>
-      <c r="W621" t="inlineStr">
+      <c r="Z621" t="inlineStr">
         <is>
           <t>51856</t>
         </is>
@@ -37595,17 +37625,17 @@
           <t>CADENA Jordi</t>
         </is>
       </c>
-      <c r="U622" t="inlineStr">
+      <c r="X622" t="inlineStr">
         <is>
           <t>51850</t>
         </is>
       </c>
-      <c r="V622" t="inlineStr">
+      <c r="Y622" t="inlineStr">
         <is>
           <t>38782</t>
         </is>
       </c>
-      <c r="W622" t="inlineStr">
+      <c r="Z622" t="inlineStr">
         <is>
           <t>41644</t>
         </is>
@@ -37683,17 +37713,17 @@
           <t>SMOLEN Michal</t>
         </is>
       </c>
-      <c r="U623" t="inlineStr">
+      <c r="X623" t="inlineStr">
         <is>
           <t>36444</t>
         </is>
       </c>
-      <c r="V623" t="inlineStr">
+      <c r="Y623" t="inlineStr">
         <is>
           <t>39898</t>
         </is>
       </c>
-      <c r="W623" t="inlineStr">
+      <c r="Z623" t="inlineStr">
         <is>
           <t>36397</t>
         </is>
@@ -37771,12 +37801,12 @@
           <t>MERRITT Jaxon</t>
         </is>
       </c>
-      <c r="U624" t="inlineStr">
+      <c r="X624" t="inlineStr">
         <is>
           <t>36537</t>
         </is>
       </c>
-      <c r="V624" t="inlineStr">
+      <c r="Y624" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
@@ -37854,17 +37884,17 @@
           <t>NEVEU Boris</t>
         </is>
       </c>
-      <c r="U625" t="inlineStr">
+      <c r="X625" t="inlineStr">
         <is>
           <t>35584</t>
         </is>
       </c>
-      <c r="V625" t="inlineStr">
+      <c r="Y625" t="inlineStr">
         <is>
           <t>35233</t>
         </is>
       </c>
-      <c r="W625" t="inlineStr">
+      <c r="Z625" t="inlineStr">
         <is>
           <t>35396</t>
         </is>
@@ -37942,17 +37972,17 @@
           <t>POPIELA Dariusz</t>
         </is>
       </c>
-      <c r="U626" t="inlineStr">
+      <c r="X626" t="inlineStr">
         <is>
           <t>35072</t>
         </is>
       </c>
-      <c r="V626" t="inlineStr">
+      <c r="Y626" t="inlineStr">
         <is>
           <t>35088</t>
         </is>
       </c>
-      <c r="W626" t="inlineStr">
+      <c r="Z626" t="inlineStr">
         <is>
           <t>35096</t>
         </is>
@@ -38030,17 +38060,17 @@
           <t>BRUS Simon</t>
         </is>
       </c>
-      <c r="U627" t="inlineStr">
+      <c r="X627" t="inlineStr">
         <is>
           <t>35589</t>
         </is>
       </c>
-      <c r="V627" t="inlineStr">
+      <c r="Y627" t="inlineStr">
         <is>
           <t>36268</t>
         </is>
       </c>
-      <c r="W627" t="inlineStr">
+      <c r="Z627" t="inlineStr">
         <is>
           <t>39076</t>
         </is>
@@ -38118,17 +38148,17 @@
           <t>TUNKA Ondrej</t>
         </is>
       </c>
-      <c r="U628" t="inlineStr">
+      <c r="X628" t="inlineStr">
         <is>
           <t>35033</t>
         </is>
       </c>
-      <c r="V628" t="inlineStr">
+      <c r="Y628" t="inlineStr">
         <is>
           <t>35031</t>
         </is>
       </c>
-      <c r="W628" t="inlineStr">
+      <c r="Z628" t="inlineStr">
         <is>
           <t>35947</t>
         </is>
@@ -38206,17 +38236,17 @@
           <t>GRIMM Alexander</t>
         </is>
       </c>
-      <c r="U629" t="inlineStr">
+      <c r="X629" t="inlineStr">
         <is>
           <t>35114</t>
         </is>
       </c>
-      <c r="V629" t="inlineStr">
+      <c r="Y629" t="inlineStr">
         <is>
           <t>35115</t>
         </is>
       </c>
-      <c r="W629" t="inlineStr">
+      <c r="Z629" t="inlineStr">
         <is>
           <t>35112</t>
         </is>
@@ -38486,7 +38516,7 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="U634" t="inlineStr">
+      <c r="X634" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -38544,7 +38574,7 @@
           <t>TAKESHITA Yuriko</t>
         </is>
       </c>
-      <c r="U635" t="inlineStr">
+      <c r="X635" t="inlineStr">
         <is>
           <t>36487</t>
         </is>
@@ -38602,7 +38632,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U636" t="inlineStr">
+      <c r="X636" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -38660,7 +38690,7 @@
           <t>NEVARILOVA Kristina</t>
         </is>
       </c>
-      <c r="U637" t="inlineStr">
+      <c r="X637" t="inlineStr">
         <is>
           <t>35467</t>
         </is>
@@ -38718,7 +38748,7 @@
           <t>LAWRENCE Rosalyn</t>
         </is>
       </c>
-      <c r="U638" t="inlineStr">
+      <c r="X638" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
@@ -38776,7 +38806,7 @@
           <t>LI Lu</t>
         </is>
       </c>
-      <c r="U639" t="inlineStr">
+      <c r="X639" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
@@ -38887,7 +38917,7 @@
           <t>PACIERPNIK Natalia</t>
         </is>
       </c>
-      <c r="U641" t="inlineStr">
+      <c r="X641" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
@@ -38945,7 +38975,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U642" t="inlineStr">
+      <c r="X642" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -39003,7 +39033,7 @@
           <t>GALUSKOVA Karolina</t>
         </is>
       </c>
-      <c r="U643" t="inlineStr">
+      <c r="X643" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
@@ -39061,7 +39091,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U644" t="inlineStr">
+      <c r="X644" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -39172,7 +39202,7 @@
           <t>LEENDERS Claudia</t>
         </is>
       </c>
-      <c r="U646" t="inlineStr">
+      <c r="X646" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
@@ -39230,7 +39260,7 @@
           <t>OBLINGER-PETERS Violetta</t>
         </is>
       </c>
-      <c r="U647" t="inlineStr">
+      <c r="X647" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
@@ -39288,7 +39318,7 @@
           <t>TERCELJ Eva</t>
         </is>
       </c>
-      <c r="U648" t="inlineStr">
+      <c r="X648" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
@@ -39346,7 +39376,7 @@
           <t>NEWMAN Nouria</t>
         </is>
       </c>
-      <c r="U649" t="inlineStr">
+      <c r="X649" t="inlineStr">
         <is>
           <t>35397</t>
         </is>
@@ -39404,7 +39434,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U650" t="inlineStr">
+      <c r="X650" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -39462,7 +39492,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U651" t="inlineStr">
+      <c r="X651" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -39520,7 +39550,7 @@
           <t>GIAI PRON Maria Clara</t>
         </is>
       </c>
-      <c r="U652" t="inlineStr">
+      <c r="X652" t="inlineStr">
         <is>
           <t>35218</t>
         </is>
@@ -39578,7 +39608,7 @@
           <t>YAZAWA Aki</t>
         </is>
       </c>
-      <c r="U653" t="inlineStr">
+      <c r="X653" t="inlineStr">
         <is>
           <t>36486</t>
         </is>
@@ -39636,7 +39666,7 @@
           <t>BOUZIDI Carole</t>
         </is>
       </c>
-      <c r="U654" t="inlineStr">
+      <c r="X654" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
@@ -39747,7 +39777,7 @@
           <t>VOJTOVA Veronika</t>
         </is>
       </c>
-      <c r="U656" t="inlineStr">
+      <c r="X656" t="inlineStr">
         <is>
           <t>35945</t>
         </is>
@@ -39858,7 +39888,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U658" t="inlineStr">
+      <c r="X658" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -39916,7 +39946,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U659" t="inlineStr">
+      <c r="X659" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -39974,7 +40004,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U660" t="inlineStr">
+      <c r="X660" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -40032,7 +40062,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U661" t="inlineStr">
+      <c r="X661" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -40090,7 +40120,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U662" t="inlineStr">
+      <c r="X662" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -40148,7 +40178,7 @@
           <t>KUHNLE Corinna</t>
         </is>
       </c>
-      <c r="U663" t="inlineStr">
+      <c r="X663" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
@@ -40211,12 +40241,12 @@
           <t>CHEN Jin</t>
         </is>
       </c>
-      <c r="U664" t="inlineStr">
+      <c r="X664" t="inlineStr">
         <is>
           <t>42237</t>
         </is>
       </c>
-      <c r="V664" t="inlineStr">
+      <c r="Y664" t="inlineStr">
         <is>
           <t>42238</t>
         </is>
@@ -40279,12 +40309,12 @@
           <t>HUANG Yongze</t>
         </is>
       </c>
-      <c r="U665" t="inlineStr">
+      <c r="X665" t="inlineStr">
         <is>
           <t>52028</t>
         </is>
       </c>
-      <c r="V665" t="inlineStr">
+      <c r="Y665" t="inlineStr">
         <is>
           <t>52029</t>
         </is>
@@ -40347,12 +40377,12 @@
           <t>USHAKOV Artem</t>
         </is>
       </c>
-      <c r="U666" t="inlineStr">
+      <c r="X666" t="inlineStr">
         <is>
           <t>35454</t>
         </is>
       </c>
-      <c r="V666" t="inlineStr">
+      <c r="Y666" t="inlineStr">
         <is>
           <t>35455</t>
         </is>
@@ -40415,12 +40445,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U667" t="inlineStr">
+      <c r="X667" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V667" t="inlineStr">
+      <c r="Y667" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -40483,12 +40513,12 @@
           <t>SKAKALA Juraj</t>
         </is>
       </c>
-      <c r="U668" t="inlineStr">
+      <c r="X668" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
       </c>
-      <c r="V668" t="inlineStr">
+      <c r="Y668" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
@@ -40551,12 +40581,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U669" t="inlineStr">
+      <c r="X669" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V669" t="inlineStr">
+      <c r="Y669" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -40619,7 +40649,7 @@
           <t>HOUNSLOW Richard</t>
         </is>
       </c>
-      <c r="U670" t="inlineStr">
+      <c r="X670" t="inlineStr">
         <is>
           <t>35634</t>
         </is>
@@ -40682,12 +40712,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U671" t="inlineStr">
+      <c r="X671" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V671" t="inlineStr">
+      <c r="Y671" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -40750,12 +40780,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U672" t="inlineStr">
+      <c r="X672" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V672" t="inlineStr">
+      <c r="Y672" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -40818,12 +40848,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U673" t="inlineStr">
+      <c r="X673" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V673" t="inlineStr">
+      <c r="Y673" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -40886,12 +40916,12 @@
           <t>PESCHIER Nicolas</t>
         </is>
       </c>
-      <c r="U674" t="inlineStr">
+      <c r="X674" t="inlineStr">
         <is>
           <t>35351</t>
         </is>
       </c>
-      <c r="V674" t="inlineStr">
+      <c r="Y674" t="inlineStr">
         <is>
           <t>35401</t>
         </is>
@@ -40954,12 +40984,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U675" t="inlineStr">
+      <c r="X675" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V675" t="inlineStr">
+      <c r="Y675" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -41022,12 +41052,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U676" t="inlineStr">
+      <c r="X676" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V676" t="inlineStr">
+      <c r="Y676" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -41090,12 +41120,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U677" t="inlineStr">
+      <c r="X677" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V677" t="inlineStr">
+      <c r="Y677" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -41158,12 +41188,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U678" t="inlineStr">
+      <c r="X678" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V678" t="inlineStr">
+      <c r="Y678" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -41226,12 +41256,12 @@
           <t>BETTGE Nico</t>
         </is>
       </c>
-      <c r="U679" t="inlineStr">
+      <c r="X679" t="inlineStr">
         <is>
           <t>35145</t>
         </is>
       </c>
-      <c r="V679" t="inlineStr">
+      <c r="Y679" t="inlineStr">
         <is>
           <t>35133</t>
         </is>
@@ -41352,12 +41382,12 @@
           <t>TALJAT Saso</t>
         </is>
       </c>
-      <c r="U681" t="inlineStr">
+      <c r="X681" t="inlineStr">
         <is>
           <t>36269</t>
         </is>
       </c>
-      <c r="V681" t="inlineStr">
+      <c r="Y681" t="inlineStr">
         <is>
           <t>36270</t>
         </is>
@@ -41420,12 +41450,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U682" t="inlineStr">
+      <c r="X682" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V682" t="inlineStr">
+      <c r="Y682" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -41488,12 +41518,12 @@
           <t>MAJERCZAK Grzegorz</t>
         </is>
       </c>
-      <c r="U683" t="inlineStr">
+      <c r="X683" t="inlineStr">
         <is>
           <t>35085</t>
         </is>
       </c>
-      <c r="V683" t="inlineStr">
+      <c r="Y683" t="inlineStr">
         <is>
           <t>35086</t>
         </is>
@@ -41561,7 +41591,7 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U684" t="inlineStr">
+      <c r="X684" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -41629,7 +41659,7 @@
           <t>DUKATOVA Jana</t>
         </is>
       </c>
-      <c r="U685" t="inlineStr">
+      <c r="X685" t="inlineStr">
         <is>
           <t>35354</t>
         </is>
@@ -41760,7 +41790,7 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U687" t="inlineStr">
+      <c r="X687" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -41828,7 +41858,7 @@
           <t>KUDEJOVA Katerina</t>
         </is>
       </c>
-      <c r="U688" t="inlineStr">
+      <c r="X688" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
@@ -41896,7 +41926,7 @@
           <t>HORN Stefanie</t>
         </is>
       </c>
-      <c r="U689" t="inlineStr">
+      <c r="X689" t="inlineStr">
         <is>
           <t>38417</t>
         </is>
@@ -41964,7 +41994,7 @@
           <t>KRAGELJ Ursa</t>
         </is>
       </c>
-      <c r="U690" t="inlineStr">
+      <c r="X690" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
@@ -42032,7 +42062,7 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U691" t="inlineStr">
+      <c r="X691" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -42100,7 +42130,7 @@
           <t>SCHORNBERG Jasmin</t>
         </is>
       </c>
-      <c r="U692" t="inlineStr">
+      <c r="X692" t="inlineStr">
         <is>
           <t>35206</t>
         </is>
@@ -42168,7 +42198,7 @@
           <t>FUNK Ricarda</t>
         </is>
       </c>
-      <c r="U693" t="inlineStr">
+      <c r="X693" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
@@ -42241,12 +42271,12 @@
           <t>BENZIEN Jan</t>
         </is>
       </c>
-      <c r="U694" t="inlineStr">
+      <c r="X694" t="inlineStr">
         <is>
           <t>35137</t>
         </is>
       </c>
-      <c r="V694" t="inlineStr">
+      <c r="Y694" t="inlineStr">
         <is>
           <t>35134</t>
         </is>
@@ -42319,12 +42349,12 @@
           <t>SKANTAR Peter</t>
         </is>
       </c>
-      <c r="U695" t="inlineStr">
+      <c r="X695" t="inlineStr">
         <is>
           <t>35360</t>
         </is>
       </c>
-      <c r="V695" t="inlineStr">
+      <c r="Y695" t="inlineStr">
         <is>
           <t>35361</t>
         </is>
@@ -42397,12 +42427,12 @@
           <t>JANE Jakub</t>
         </is>
       </c>
-      <c r="U696" t="inlineStr">
+      <c r="X696" t="inlineStr">
         <is>
           <t>35060</t>
         </is>
       </c>
-      <c r="V696" t="inlineStr">
+      <c r="Y696" t="inlineStr">
         <is>
           <t>35061</t>
         </is>
@@ -42475,12 +42505,12 @@
           <t>PECHE Matthieu</t>
         </is>
       </c>
-      <c r="U697" t="inlineStr">
+      <c r="X697" t="inlineStr">
         <is>
           <t>35350</t>
         </is>
       </c>
-      <c r="V697" t="inlineStr">
+      <c r="Y697" t="inlineStr">
         <is>
           <t>35400</t>
         </is>
@@ -42553,12 +42583,12 @@
           <t>BATIK Jan</t>
         </is>
       </c>
-      <c r="U698" t="inlineStr">
+      <c r="X698" t="inlineStr">
         <is>
           <t>35368</t>
         </is>
       </c>
-      <c r="V698" t="inlineStr">
+      <c r="Y698" t="inlineStr">
         <is>
           <t>35367</t>
         </is>
@@ -42631,12 +42661,12 @@
           <t>SINDLER Marek</t>
         </is>
       </c>
-      <c r="U699" t="inlineStr">
+      <c r="X699" t="inlineStr">
         <is>
           <t>35062</t>
         </is>
       </c>
-      <c r="V699" t="inlineStr">
+      <c r="Y699" t="inlineStr">
         <is>
           <t>35063</t>
         </is>
@@ -42709,12 +42739,12 @@
           <t>POCHWALA Marcin</t>
         </is>
       </c>
-      <c r="U700" t="inlineStr">
+      <c r="X700" t="inlineStr">
         <is>
           <t>35080</t>
         </is>
       </c>
-      <c r="V700" t="inlineStr">
+      <c r="Y700" t="inlineStr">
         <is>
           <t>35079</t>
         </is>
@@ -42787,12 +42817,12 @@
           <t>BISO Hugo</t>
         </is>
       </c>
-      <c r="U701" t="inlineStr">
+      <c r="X701" t="inlineStr">
         <is>
           <t>35403</t>
         </is>
       </c>
-      <c r="V701" t="inlineStr">
+      <c r="Y701" t="inlineStr">
         <is>
           <t>35229</t>
         </is>
@@ -42865,12 +42895,12 @@
           <t>BECKER Thomas</t>
         </is>
       </c>
-      <c r="U702" t="inlineStr">
+      <c r="X702" t="inlineStr">
         <is>
           <t>35139</t>
         </is>
       </c>
-      <c r="V702" t="inlineStr">
+      <c r="Y702" t="inlineStr">
         <is>
           <t>35143</t>
         </is>
@@ -42943,12 +42973,12 @@
           <t>VRZAN Jakub</t>
         </is>
       </c>
-      <c r="U703" t="inlineStr">
+      <c r="X703" t="inlineStr">
         <is>
           <t>35042</t>
         </is>
       </c>
-      <c r="V703" t="inlineStr">
+      <c r="Y703" t="inlineStr">
         <is>
           <t>35043</t>
         </is>
@@ -43026,17 +43056,17 @@
           <t>CHEN Shi</t>
         </is>
       </c>
-      <c r="U704" t="inlineStr">
+      <c r="X704" t="inlineStr">
         <is>
           <t>37086</t>
         </is>
       </c>
-      <c r="V704" t="inlineStr">
+      <c r="Y704" t="inlineStr">
         <is>
           <t>52023</t>
         </is>
       </c>
-      <c r="W704" t="inlineStr">
+      <c r="Z704" t="inlineStr">
         <is>
           <t>52027</t>
         </is>
@@ -43104,12 +43134,12 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U705" t="inlineStr">
+      <c r="X705" t="inlineStr">
         <is>
           <t>35331</t>
         </is>
       </c>
-      <c r="W705" t="inlineStr">
+      <c r="Z705" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -43177,17 +43207,17 @@
           <t>DENHOLLANDER Jazmyne</t>
         </is>
       </c>
-      <c r="U706" t="inlineStr">
+      <c r="X706" t="inlineStr">
         <is>
           <t>35542</t>
         </is>
       </c>
-      <c r="V706" t="inlineStr">
+      <c r="Y706" t="inlineStr">
         <is>
           <t>35533</t>
         </is>
       </c>
-      <c r="W706" t="inlineStr">
+      <c r="Z706" t="inlineStr">
         <is>
           <t>37165</t>
         </is>
@@ -43265,12 +43295,12 @@
           <t>CWIK Sara</t>
         </is>
       </c>
-      <c r="U707" t="inlineStr">
+      <c r="X707" t="inlineStr">
         <is>
           <t>35077</t>
         </is>
       </c>
-      <c r="W707" t="inlineStr">
+      <c r="Z707" t="inlineStr">
         <is>
           <t>43978</t>
         </is>
@@ -43348,17 +43378,17 @@
           <t>NOVAK Ajda</t>
         </is>
       </c>
-      <c r="U708" t="inlineStr">
+      <c r="X708" t="inlineStr">
         <is>
           <t>36264</t>
         </is>
       </c>
-      <c r="V708" t="inlineStr">
+      <c r="Y708" t="inlineStr">
         <is>
           <t>36263</t>
         </is>
       </c>
-      <c r="W708" t="inlineStr">
+      <c r="Z708" t="inlineStr">
         <is>
           <t>39079</t>
         </is>
@@ -43426,17 +43456,17 @@
           <t>LEITNER Lisa</t>
         </is>
       </c>
-      <c r="U709" t="inlineStr">
+      <c r="X709" t="inlineStr">
         <is>
           <t>35289</t>
         </is>
       </c>
-      <c r="V709" t="inlineStr">
+      <c r="Y709" t="inlineStr">
         <is>
           <t>35282</t>
         </is>
       </c>
-      <c r="W709" t="inlineStr">
+      <c r="Z709" t="inlineStr">
         <is>
           <t>35305</t>
         </is>
@@ -43514,17 +43544,17 @@
           <t>OLAZABAL Klara</t>
         </is>
       </c>
-      <c r="U710" t="inlineStr">
+      <c r="X710" t="inlineStr">
         <is>
           <t>35764</t>
         </is>
       </c>
-      <c r="V710" t="inlineStr">
+      <c r="Y710" t="inlineStr">
         <is>
           <t>51854</t>
         </is>
       </c>
-      <c r="W710" t="inlineStr">
+      <c r="Z710" t="inlineStr">
         <is>
           <t>43985</t>
         </is>
@@ -43602,12 +43632,12 @@
           <t>BORROWS Alison</t>
         </is>
       </c>
-      <c r="V711" t="inlineStr">
+      <c r="Y711" t="inlineStr">
         <is>
           <t>36531</t>
         </is>
       </c>
-      <c r="W711" t="inlineStr">
+      <c r="Z711" t="inlineStr">
         <is>
           <t>38440</t>
         </is>
@@ -43685,17 +43715,17 @@
           <t>HILGERTOVA Stepanka</t>
         </is>
       </c>
-      <c r="U712" t="inlineStr">
+      <c r="X712" t="inlineStr">
         <is>
           <t>37266</t>
         </is>
       </c>
-      <c r="V712" t="inlineStr">
+      <c r="Y712" t="inlineStr">
         <is>
           <t>35034</t>
         </is>
       </c>
-      <c r="W712" t="inlineStr">
+      <c r="Z712" t="inlineStr">
         <is>
           <t>35035</t>
         </is>
@@ -43763,17 +43793,17 @@
           <t>FER Emilie</t>
         </is>
       </c>
-      <c r="U713" t="inlineStr">
+      <c r="X713" t="inlineStr">
         <is>
           <t>35231</t>
         </is>
       </c>
-      <c r="V713" t="inlineStr">
+      <c r="Y713" t="inlineStr">
         <is>
           <t>35397</t>
         </is>
       </c>
-      <c r="W713" t="inlineStr">
+      <c r="Z713" t="inlineStr">
         <is>
           <t>35314</t>
         </is>
@@ -43851,12 +43881,12 @@
           <t>FRITSCHE Lisa</t>
         </is>
       </c>
-      <c r="V714" t="inlineStr">
+      <c r="Y714" t="inlineStr">
         <is>
           <t>35122</t>
         </is>
       </c>
-      <c r="W714" t="inlineStr">
+      <c r="Z714" t="inlineStr">
         <is>
           <t>39883</t>
         </is>
@@ -43921,17 +43951,62 @@
       </c>
       <c r="R715" t="inlineStr">
         <is>
-          <t>KARLOVSKY Ondrej/JANE Jakub</t>
+          <t>KARLOVSKY Ondrej</t>
         </is>
       </c>
       <c r="S715" t="inlineStr">
         <is>
-          <t>KASPAR Jonas/SINDLER Marek</t>
+          <t>JANE Jakub</t>
         </is>
       </c>
       <c r="T715" t="inlineStr">
         <is>
-          <t>KOPLIK Tomas/VRZAN Jakub</t>
+          <t>KASPAR Jonas</t>
+        </is>
+      </c>
+      <c r="U715" t="inlineStr">
+        <is>
+          <t>SINDLER Marek</t>
+        </is>
+      </c>
+      <c r="V715" t="inlineStr">
+        <is>
+          <t>KOPLIK Tomas</t>
+        </is>
+      </c>
+      <c r="W715" t="inlineStr">
+        <is>
+          <t>VRZAN Jakub</t>
+        </is>
+      </c>
+      <c r="X715" t="inlineStr">
+        <is>
+          <t>35060</t>
+        </is>
+      </c>
+      <c r="Y715" t="inlineStr">
+        <is>
+          <t>35061</t>
+        </is>
+      </c>
+      <c r="Z715" t="inlineStr">
+        <is>
+          <t>35062</t>
+        </is>
+      </c>
+      <c r="AA715" t="inlineStr">
+        <is>
+          <t>35063</t>
+        </is>
+      </c>
+      <c r="AB715" t="inlineStr">
+        <is>
+          <t>35042</t>
+        </is>
+      </c>
+      <c r="AC715" t="inlineStr">
+        <is>
+          <t>35043</t>
         </is>
       </c>
     </row>
@@ -43994,17 +44069,62 @@
       </c>
       <c r="R716" t="inlineStr">
         <is>
-          <t>SZCZEPANSKI Piotr/POCHWALA Marcin</t>
+          <t>SZCZEPANSKI Piotr</t>
         </is>
       </c>
       <c r="S716" t="inlineStr">
         <is>
-          <t>BRZEZINSKI Filip/BRZEZINSKI Andrzej</t>
+          <t>POCHWALA Marcin</t>
         </is>
       </c>
       <c r="T716" t="inlineStr">
         <is>
-          <t>WIERCIOCH Michal/MAJERCZAK Grzegorz</t>
+          <t>BRZEZINSKI Filip</t>
+        </is>
+      </c>
+      <c r="U716" t="inlineStr">
+        <is>
+          <t>BRZEZINSKI Andrzej</t>
+        </is>
+      </c>
+      <c r="V716" t="inlineStr">
+        <is>
+          <t>WIERCIOCH Michal</t>
+        </is>
+      </c>
+      <c r="W716" t="inlineStr">
+        <is>
+          <t>MAJERCZAK Grzegorz</t>
+        </is>
+      </c>
+      <c r="X716" t="inlineStr">
+        <is>
+          <t>35080</t>
+        </is>
+      </c>
+      <c r="Y716" t="inlineStr">
+        <is>
+          <t>35079</t>
+        </is>
+      </c>
+      <c r="Z716" t="inlineStr">
+        <is>
+          <t>35082</t>
+        </is>
+      </c>
+      <c r="AA716" t="inlineStr">
+        <is>
+          <t>35081</t>
+        </is>
+      </c>
+      <c r="AB716" t="inlineStr">
+        <is>
+          <t>35085</t>
+        </is>
+      </c>
+      <c r="AC716" t="inlineStr">
+        <is>
+          <t>35086</t>
         </is>
       </c>
     </row>
@@ -44057,17 +44177,42 @@
       </c>
       <c r="R717" t="inlineStr">
         <is>
-          <t>FLORENCE David/HOUNSLOW Richard</t>
+          <t>FLORENCE David</t>
         </is>
       </c>
       <c r="S717" t="inlineStr">
         <is>
-          <t>PROCTOR Mark/STOTT Etienne</t>
+          <t>HOUNSLOW Richard</t>
         </is>
       </c>
       <c r="T717" t="inlineStr">
         <is>
-          <t>BURGESS Adam/PITT Greg</t>
+          <t>PROCTOR Mark</t>
+        </is>
+      </c>
+      <c r="U717" t="inlineStr">
+        <is>
+          <t>STOTT Etienne</t>
+        </is>
+      </c>
+      <c r="V717" t="inlineStr">
+        <is>
+          <t>BURGESS Adam</t>
+        </is>
+      </c>
+      <c r="W717" t="inlineStr">
+        <is>
+          <t>PITT Greg</t>
+        </is>
+      </c>
+      <c r="X717" t="inlineStr">
+        <is>
+          <t>35634</t>
+        </is>
+      </c>
+      <c r="AB717" t="inlineStr">
+        <is>
+          <t>35647</t>
         </is>
       </c>
     </row>
@@ -44130,17 +44275,62 @@
       </c>
       <c r="R718" t="inlineStr">
         <is>
-          <t>ANTON Franz/BENZIEN Jan</t>
+          <t>ANTON Franz</t>
         </is>
       </c>
       <c r="S718" t="inlineStr">
         <is>
-          <t>BEHLING Robert/BECKER Thomas</t>
+          <t>BENZIEN Jan</t>
         </is>
       </c>
       <c r="T718" t="inlineStr">
         <is>
-          <t>MUELLER Kai/MUELLER Kevin</t>
+          <t>BEHLING Robert</t>
+        </is>
+      </c>
+      <c r="U718" t="inlineStr">
+        <is>
+          <t>BECKER Thomas</t>
+        </is>
+      </c>
+      <c r="V718" t="inlineStr">
+        <is>
+          <t>MUELLER Kai</t>
+        </is>
+      </c>
+      <c r="W718" t="inlineStr">
+        <is>
+          <t>MUELLER Kevin</t>
+        </is>
+      </c>
+      <c r="X718" t="inlineStr">
+        <is>
+          <t>35137</t>
+        </is>
+      </c>
+      <c r="Y718" t="inlineStr">
+        <is>
+          <t>35134</t>
+        </is>
+      </c>
+      <c r="Z718" t="inlineStr">
+        <is>
+          <t>35139</t>
+        </is>
+      </c>
+      <c r="AA718" t="inlineStr">
+        <is>
+          <t>35143</t>
+        </is>
+      </c>
+      <c r="AB718" t="inlineStr">
+        <is>
+          <t>35148</t>
+        </is>
+      </c>
+      <c r="AC718" t="inlineStr">
+        <is>
+          <t>35149</t>
         </is>
       </c>
     </row>
@@ -44203,17 +44393,62 @@
       </c>
       <c r="R719" t="inlineStr">
         <is>
-          <t>PICCO Pierre/BISO Hugo</t>
+          <t>PICCO Pierre</t>
         </is>
       </c>
       <c r="S719" t="inlineStr">
         <is>
-          <t>KLAUSS Gauthier/PECHE Matthieu</t>
+          <t>BISO Hugo</t>
         </is>
       </c>
       <c r="T719" t="inlineStr">
         <is>
-          <t>PRIGENT Yves/KERVELLA Loic</t>
+          <t>KLAUSS Gauthier</t>
+        </is>
+      </c>
+      <c r="U719" t="inlineStr">
+        <is>
+          <t>PECHE Matthieu</t>
+        </is>
+      </c>
+      <c r="V719" t="inlineStr">
+        <is>
+          <t>PRIGENT Yves</t>
+        </is>
+      </c>
+      <c r="W719" t="inlineStr">
+        <is>
+          <t>KERVELLA Loic</t>
+        </is>
+      </c>
+      <c r="X719" t="inlineStr">
+        <is>
+          <t>35403</t>
+        </is>
+      </c>
+      <c r="Y719" t="inlineStr">
+        <is>
+          <t>35229</t>
+        </is>
+      </c>
+      <c r="Z719" t="inlineStr">
+        <is>
+          <t>35350</t>
+        </is>
+      </c>
+      <c r="AA719" t="inlineStr">
+        <is>
+          <t>35400</t>
+        </is>
+      </c>
+      <c r="AB719" t="inlineStr">
+        <is>
+          <t>35671</t>
+        </is>
+      </c>
+      <c r="AC719" t="inlineStr">
+        <is>
+          <t>35672</t>
         </is>
       </c>
     </row>
